--- a/experiments/03_dataset_comparison/report/dev_v1_proper_term_across_expansion_modes.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_proper_term_across_expansion_modes.xlsx
@@ -555,32 +555,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/03_dataset_comparison/report/dev_v1_proper_term_across_expansion_modes.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_proper_term_across_expansion_modes.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,26 +42,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9C2E9"/>
-        <bgColor rgb="FFD9C2E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFF8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -165,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,16 +167,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +811,7 @@
       <c r="P3" s="5" t="n">
         <v>70.56000000000002</v>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -843,7 +828,7 @@
       <c r="U3" s="5" t="n">
         <v>0.9288117048923646</v>
       </c>
-      <c r="V3" s="7" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -860,14 +845,14 @@
       <c r="Z3" s="5" t="n">
         <v>0.8423390081421178</v>
       </c>
-      <c r="AA3" s="7" t="inlineStr">
+      <c r="AA3" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>enru</t>
@@ -902,7 +887,7 @@
       <c r="K4" s="5" t="n">
         <v>72.45995024990887</v>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>expand</t>
         </is>
@@ -919,7 +904,7 @@
       <c r="P4" s="5" t="n">
         <v>73.90393294648615</v>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -936,7 +921,7 @@
       <c r="U4" s="5" t="n">
         <v>0.929763008632753</v>
       </c>
-      <c r="V4" s="7" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -953,7 +938,7 @@
       <c r="Z4" s="5" t="n">
         <v>0.774401473296503</v>
       </c>
-      <c r="AA4" s="7" t="inlineStr">
+      <c r="AA4" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -978,7 +963,7 @@
       <c r="F5" s="5" t="n">
         <v>64.83165350095547</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>expand</t>
         </is>
@@ -1012,7 +997,7 @@
       <c r="P5" s="5" t="n">
         <v>92.94871794871796</v>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -1029,7 +1014,7 @@
       <c r="U5" s="5" t="n">
         <v>0.9527865808420228</v>
       </c>
-      <c r="V5" s="7" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
@@ -1046,7 +1031,7 @@
       <c r="Z5" s="5" t="n">
         <v>0.8671814671814662</v>
       </c>
-      <c r="AA5" s="7" t="inlineStr">
+      <c r="AA5" s="6" t="inlineStr">
         <is>
           <t>cleaned</t>
         </is>
